--- a/slide_classification/TCGA_Results/Averaging/UNI2/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
+++ b/slide_classification/TCGA_Results/Averaging/UNI2/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
@@ -517,7 +517,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.095628</v>
+        <v>0.31056</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -560,7 +560,7 @@
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.995937</v>
+        <v>0.994113</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -603,7 +603,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.322956</v>
+        <v>0.166728</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -646,7 +646,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.334495</v>
+        <v>0.369478</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -689,7 +689,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.211016</v>
+        <v>0.324054</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -732,7 +732,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.275665</v>
+        <v>0.325102</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -775,7 +775,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.322093</v>
+        <v>0.270037</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -818,7 +818,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.09059499999999999</v>
+        <v>0.038309</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.229876</v>
+        <v>0.318425</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -904,7 +904,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.123794</v>
+        <v>0.163139</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -947,7 +947,7 @@
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>0.950677</v>
+        <v>0.996802</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -990,7 +990,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.25364</v>
+        <v>0.202235</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1033,7 +1033,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.258878</v>
+        <v>0.213687</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1076,7 +1076,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.153959</v>
+        <v>0.138425</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1119,7 +1119,7 @@
         <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>0.894926</v>
+        <v>0.880826</v>
       </c>
       <c r="H16" t="n">
         <v>1</v>
@@ -1162,7 +1162,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.152873</v>
+        <v>0.1126</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1205,7 +1205,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.126731</v>
+        <v>0.091709</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1248,7 +1248,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.199337</v>
+        <v>0.12344</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1291,7 +1291,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.16932</v>
+        <v>0.085572</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.163267</v>
+        <v>0.142346</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1377,7 +1377,7 @@
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>0.989966</v>
+        <v>0.976591</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1420,7 +1420,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.101063</v>
+        <v>0.095053</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1463,7 +1463,7 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.143104</v>
+        <v>0.178238</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1506,7 +1506,7 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.186769</v>
+        <v>0.191454</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1549,7 +1549,7 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0.260044</v>
+        <v>0.268385</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.255943</v>
+        <v>0.232904</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1635,7 +1635,7 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.254628</v>
+        <v>0.149555</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1678,7 +1678,7 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.390011</v>
+        <v>0.37345</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1721,7 +1721,7 @@
         <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>0.995983</v>
+        <v>0.992668</v>
       </c>
       <c r="H30" t="n">
         <v>1</v>
@@ -1764,7 +1764,7 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.143974</v>
+        <v>0.07996</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1807,7 +1807,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.263499</v>
+        <v>0.197537</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1850,7 +1850,7 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.22999</v>
+        <v>0.28918</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1893,7 +1893,7 @@
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.105481</v>
+        <v>0.07686</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1936,7 +1936,7 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>0.088314</v>
+        <v>0.118893</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1979,7 +1979,7 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0.048888</v>
+        <v>0.120607</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -2022,7 +2022,7 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0.32168</v>
+        <v>0.302552</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -2065,7 +2065,7 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0.161921</v>
+        <v>0.143405</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2108,7 +2108,7 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0.170578</v>
+        <v>0.134674</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -2151,7 +2151,7 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0.217128</v>
+        <v>0.182399</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0.104436</v>
+        <v>0.172003</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0.119966</v>
+        <v>0.06764199999999999</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -2280,7 +2280,7 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0.20522</v>
+        <v>0.123684</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0.48395</v>
+        <v>0.409613</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -2366,7 +2366,7 @@
         <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>0.778593</v>
+        <v>0.870738</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -2409,7 +2409,7 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>0.43782</v>
+        <v>0.403507</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -2452,7 +2452,7 @@
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>0.184372</v>
+        <v>0.138871</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -2495,7 +2495,7 @@
         <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>0.509549</v>
+        <v>0.643541</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -2538,7 +2538,7 @@
         <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>0.158569</v>
+        <v>0.091096</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -2581,7 +2581,7 @@
         <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>0.88729</v>
+        <v>0.828066</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -2624,7 +2624,7 @@
         <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>0.420214</v>
+        <v>0.152643</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -2667,7 +2667,7 @@
         <v>1</v>
       </c>
       <c r="G52" t="n">
-        <v>0.99099</v>
+        <v>0.9899210000000001</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -2710,7 +2710,7 @@
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>0.447577</v>
+        <v>0.168089</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -2753,7 +2753,7 @@
         <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>0.287675</v>
+        <v>0.234689</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -2793,10 +2793,10 @@
         <v>0.369329</v>
       </c>
       <c r="F55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>0.561737</v>
+        <v>0.259015</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -2839,7 +2839,7 @@
         <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>0.170599</v>
+        <v>0.110601</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
         <v>1</v>
       </c>
       <c r="G57" t="n">
-        <v>0.826469</v>
+        <v>0.694794</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -2925,7 +2925,7 @@
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>0.152382</v>
+        <v>0.078926</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0.000164</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G59" t="n">
-        <v>0.470172</v>
+        <v>0.750126</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -3011,7 +3011,7 @@
         <v>1</v>
       </c>
       <c r="G60" t="n">
-        <v>0.966611</v>
+        <v>0.8200730000000001</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
         <v>1</v>
       </c>
       <c r="G61" t="n">
-        <v>0.998289</v>
+        <v>0.987024</v>
       </c>
       <c r="H61" t="n">
         <v>1</v>
@@ -3094,10 +3094,10 @@
         <v>0.022667</v>
       </c>
       <c r="F62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>0.526068</v>
+        <v>0.148404</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
@@ -3140,7 +3140,7 @@
         <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>0.881462</v>
+        <v>0.915197</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -3183,7 +3183,7 @@
         <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>0.347609</v>
+        <v>0.307516</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
@@ -3226,7 +3226,7 @@
         <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>0.349939</v>
+        <v>0.295163</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -3269,7 +3269,7 @@
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>0.12183</v>
+        <v>0.140031</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -3312,7 +3312,7 @@
         <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>0.195462</v>
+        <v>0.169027</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -3355,7 +3355,7 @@
         <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>0.273981</v>
+        <v>0.273744</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -3398,7 +3398,7 @@
         <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>0.114356</v>
+        <v>0.053049</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -3441,7 +3441,7 @@
         <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>0.138642</v>
+        <v>0.127316</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -3484,7 +3484,7 @@
         <v>1</v>
       </c>
       <c r="G71" t="n">
-        <v>0.920051</v>
+        <v>0.771225</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -3527,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>0.16303</v>
+        <v>0.102409</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -3567,10 +3567,10 @@
         <v>0.019118</v>
       </c>
       <c r="F73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>0.519588</v>
+        <v>0.332456</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -3613,7 +3613,7 @@
         <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>0.143554</v>
+        <v>0.175405</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -3656,7 +3656,7 @@
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>0.261242</v>
+        <v>0.136779</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -3699,7 +3699,7 @@
         <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>0.177584</v>
+        <v>0.152928</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -3742,7 +3742,7 @@
         <v>1</v>
       </c>
       <c r="G77" t="n">
-        <v>0.996938</v>
+        <v>0.998934</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -3785,7 +3785,7 @@
         <v>1</v>
       </c>
       <c r="G78" t="n">
-        <v>0.8682609999999999</v>
+        <v>0.954537</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
@@ -3828,7 +3828,7 @@
         <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>0.288717</v>
+        <v>0.388739</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
@@ -3871,7 +3871,7 @@
         <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>0.11093</v>
+        <v>0.239702</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -3914,7 +3914,7 @@
         <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>0.151186</v>
+        <v>0.104181</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -3954,10 +3954,10 @@
         <v>0.006205</v>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G82" t="n">
-        <v>0.399607</v>
+        <v>0.604222</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
@@ -3997,10 +3997,10 @@
         <v>0.005696</v>
       </c>
       <c r="F83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G83" t="n">
-        <v>0.315344</v>
+        <v>0.661009</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -4043,7 +4043,7 @@
         <v>0</v>
       </c>
       <c r="G84" t="n">
-        <v>0.08386299999999999</v>
+        <v>0.194363</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -4086,7 +4086,7 @@
         <v>0</v>
       </c>
       <c r="G85" t="n">
-        <v>0.252603</v>
+        <v>0.4323</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
@@ -4129,7 +4129,7 @@
         <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>0.351591</v>
+        <v>0.281862</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -4172,7 +4172,7 @@
         <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>0.09571200000000001</v>
+        <v>0.254266</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -4215,7 +4215,7 @@
         <v>0</v>
       </c>
       <c r="G88" t="n">
-        <v>0.093654</v>
+        <v>0.101893</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -4258,7 +4258,7 @@
         <v>1</v>
       </c>
       <c r="G89" t="n">
-        <v>0.979741</v>
+        <v>0.987172</v>
       </c>
       <c r="H89" t="n">
         <v>1</v>
@@ -4301,7 +4301,7 @@
         <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>0.047287</v>
+        <v>0.046628</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>0.06519999999999999</v>
+        <v>0.038994</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -4387,7 +4387,7 @@
         <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>0.091461</v>
+        <v>0.144387</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
@@ -4430,7 +4430,7 @@
         <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>0.204595</v>
+        <v>0.237123</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -4473,7 +4473,7 @@
         <v>0</v>
       </c>
       <c r="G94" t="n">
-        <v>0.146295</v>
+        <v>0.100426</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>0</v>
       </c>
       <c r="G95" t="n">
-        <v>0.102702</v>
+        <v>0.094748</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -4559,7 +4559,7 @@
         <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>0.220106</v>
+        <v>0.157354</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -4602,7 +4602,7 @@
         <v>0</v>
       </c>
       <c r="G97" t="n">
-        <v>0.160519</v>
+        <v>0.133674</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
@@ -4645,7 +4645,7 @@
         <v>1</v>
       </c>
       <c r="G98" t="n">
-        <v>0.83291</v>
+        <v>0.811234</v>
       </c>
       <c r="H98" t="n">
         <v>0</v>
@@ -4688,7 +4688,7 @@
         <v>1</v>
       </c>
       <c r="G99" t="n">
-        <v>0.83538</v>
+        <v>0.557273</v>
       </c>
       <c r="H99" t="n">
         <v>0</v>
@@ -4731,7 +4731,7 @@
         <v>0</v>
       </c>
       <c r="G100" t="n">
-        <v>0.1686</v>
+        <v>0.075961</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
@@ -4774,7 +4774,7 @@
         <v>1</v>
       </c>
       <c r="G101" t="n">
-        <v>0.996737</v>
+        <v>0.985861</v>
       </c>
       <c r="H101" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
         <v>1</v>
       </c>
       <c r="G102" t="n">
-        <v>0.998994</v>
+        <v>0.997615</v>
       </c>
       <c r="H102" t="n">
         <v>0</v>
@@ -4860,7 +4860,7 @@
         <v>0</v>
       </c>
       <c r="G103" t="n">
-        <v>0.176254</v>
+        <v>0.25065</v>
       </c>
       <c r="H103" t="n">
         <v>0</v>
@@ -4903,7 +4903,7 @@
         <v>0</v>
       </c>
       <c r="G104" t="n">
-        <v>0.324269</v>
+        <v>0.088572</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -4946,7 +4946,7 @@
         <v>0</v>
       </c>
       <c r="G105" t="n">
-        <v>0.275879</v>
+        <v>0.277848</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -4989,7 +4989,7 @@
         <v>0</v>
       </c>
       <c r="G106" t="n">
-        <v>0.458298</v>
+        <v>0.400995</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
@@ -5032,7 +5032,7 @@
         <v>0</v>
       </c>
       <c r="G107" t="n">
-        <v>0.207673</v>
+        <v>0.192914</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -5075,7 +5075,7 @@
         <v>1</v>
       </c>
       <c r="G108" t="n">
-        <v>0.980774</v>
+        <v>0.996937</v>
       </c>
       <c r="H108" t="n">
         <v>1</v>
@@ -5118,7 +5118,7 @@
         <v>0</v>
       </c>
       <c r="G109" t="n">
-        <v>0.310365</v>
+        <v>0.156153</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
@@ -5161,7 +5161,7 @@
         <v>1</v>
       </c>
       <c r="G110" t="n">
-        <v>0.891084</v>
+        <v>0.863994</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -5204,7 +5204,7 @@
         <v>0</v>
       </c>
       <c r="G111" t="n">
-        <v>0.323837</v>
+        <v>0.169911</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -5247,7 +5247,7 @@
         <v>0</v>
       </c>
       <c r="G112" t="n">
-        <v>0.229286</v>
+        <v>0.196986</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -5290,7 +5290,7 @@
         <v>0</v>
       </c>
       <c r="G113" t="n">
-        <v>0.247263</v>
+        <v>0.250037</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
@@ -5333,7 +5333,7 @@
         <v>0</v>
       </c>
       <c r="G114" t="n">
-        <v>0.191659</v>
+        <v>0.142566</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -5376,7 +5376,7 @@
         <v>0</v>
       </c>
       <c r="G115" t="n">
-        <v>0.316491</v>
+        <v>0.297295</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
@@ -5419,7 +5419,7 @@
         <v>1</v>
       </c>
       <c r="G116" t="n">
-        <v>0.647872</v>
+        <v>0.732869</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
@@ -5462,7 +5462,7 @@
         <v>0</v>
       </c>
       <c r="G117" t="n">
-        <v>0.332279</v>
+        <v>0.280851</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -5505,7 +5505,7 @@
         <v>0</v>
       </c>
       <c r="G118" t="n">
-        <v>0.168014</v>
+        <v>0.134505</v>
       </c>
       <c r="H118" t="n">
         <v>0</v>
@@ -5548,7 +5548,7 @@
         <v>1</v>
       </c>
       <c r="G119" t="n">
-        <v>0.93769</v>
+        <v>0.965974</v>
       </c>
       <c r="H119" t="n">
         <v>0</v>
@@ -5591,7 +5591,7 @@
         <v>0</v>
       </c>
       <c r="G120" t="n">
-        <v>0.181299</v>
+        <v>0.122723</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
@@ -5631,10 +5631,10 @@
         <v>0.200378</v>
       </c>
       <c r="F121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G121" t="n">
-        <v>0.478763</v>
+        <v>0.5217810000000001</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -5677,7 +5677,7 @@
         <v>1</v>
       </c>
       <c r="G122" t="n">
-        <v>0.968445</v>
+        <v>0.974225</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
@@ -5720,7 +5720,7 @@
         <v>1</v>
       </c>
       <c r="G123" t="n">
-        <v>0.833906</v>
+        <v>0.834149</v>
       </c>
       <c r="H123" t="n">
         <v>1</v>
@@ -5763,7 +5763,7 @@
         <v>0</v>
       </c>
       <c r="G124" t="n">
-        <v>0.267021</v>
+        <v>0.338614</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
@@ -5806,7 +5806,7 @@
         <v>0</v>
       </c>
       <c r="G125" t="n">
-        <v>0.189623</v>
+        <v>0.143527</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
@@ -5849,7 +5849,7 @@
         <v>0</v>
       </c>
       <c r="G126" t="n">
-        <v>0.347636</v>
+        <v>0.313951</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
@@ -5892,7 +5892,7 @@
         <v>0</v>
       </c>
       <c r="G127" t="n">
-        <v>0.172288</v>
+        <v>0.123383</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -5935,7 +5935,7 @@
         <v>0</v>
       </c>
       <c r="G128" t="n">
-        <v>0.340189</v>
+        <v>0.38339</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
         <v>1</v>
       </c>
       <c r="G129" t="n">
-        <v>0.735632</v>
+        <v>0.859242</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -6021,7 +6021,7 @@
         <v>0</v>
       </c>
       <c r="G130" t="n">
-        <v>0.271441</v>
+        <v>0.319077</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -6064,7 +6064,7 @@
         <v>0</v>
       </c>
       <c r="G131" t="n">
-        <v>0.173565</v>
+        <v>0.143608</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
@@ -6107,7 +6107,7 @@
         <v>0</v>
       </c>
       <c r="G132" t="n">
-        <v>0.299886</v>
+        <v>0.264172</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
@@ -6150,7 +6150,7 @@
         <v>0</v>
       </c>
       <c r="G133" t="n">
-        <v>0.250249</v>
+        <v>0.301655</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
@@ -6190,10 +6190,10 @@
         <v>2.2e-05</v>
       </c>
       <c r="F134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G134" t="n">
-        <v>0.5348889999999999</v>
+        <v>0.478548</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -6236,7 +6236,7 @@
         <v>0</v>
       </c>
       <c r="G135" t="n">
-        <v>0.274883</v>
+        <v>0.235078</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -6279,7 +6279,7 @@
         <v>0</v>
       </c>
       <c r="G136" t="n">
-        <v>0.259247</v>
+        <v>0.183057</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -6322,7 +6322,7 @@
         <v>0</v>
       </c>
       <c r="G137" t="n">
-        <v>0.309609</v>
+        <v>0.252682</v>
       </c>
       <c r="H137" t="n">
         <v>0</v>
@@ -6365,7 +6365,7 @@
         <v>0</v>
       </c>
       <c r="G138" t="n">
-        <v>0.219741</v>
+        <v>0.218096</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -6408,7 +6408,7 @@
         <v>1</v>
       </c>
       <c r="G139" t="n">
-        <v>0.703418</v>
+        <v>0.5453440000000001</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
@@ -6451,7 +6451,7 @@
         <v>0</v>
       </c>
       <c r="G140" t="n">
-        <v>0.113852</v>
+        <v>0.111283</v>
       </c>
       <c r="H140" t="n">
         <v>0</v>
@@ -6494,7 +6494,7 @@
         <v>1</v>
       </c>
       <c r="G141" t="n">
-        <v>0.501124</v>
+        <v>0.686527</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -6537,7 +6537,7 @@
         <v>0</v>
       </c>
       <c r="G142" t="n">
-        <v>0.2315</v>
+        <v>0.259619</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -6580,7 +6580,7 @@
         <v>0</v>
       </c>
       <c r="G143" t="n">
-        <v>0.244696</v>
+        <v>0.15306</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -6623,7 +6623,7 @@
         <v>0</v>
       </c>
       <c r="G144" t="n">
-        <v>0.247765</v>
+        <v>0.112777</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -6666,7 +6666,7 @@
         <v>0</v>
       </c>
       <c r="G145" t="n">
-        <v>0.166721</v>
+        <v>0.160739</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -6709,7 +6709,7 @@
         <v>0</v>
       </c>
       <c r="G146" t="n">
-        <v>0.138255</v>
+        <v>0.153384</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
@@ -6752,7 +6752,7 @@
         <v>0</v>
       </c>
       <c r="G147" t="n">
-        <v>0.279139</v>
+        <v>0.178799</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
@@ -6795,7 +6795,7 @@
         <v>0</v>
       </c>
       <c r="G148" t="n">
-        <v>0.30906</v>
+        <v>0.086577</v>
       </c>
       <c r="H148" t="n">
         <v>0</v>
@@ -6838,7 +6838,7 @@
         <v>1</v>
       </c>
       <c r="G149" t="n">
-        <v>0.934381</v>
+        <v>0.845467</v>
       </c>
       <c r="H149" t="n">
         <v>0</v>
@@ -6881,7 +6881,7 @@
         <v>0</v>
       </c>
       <c r="G150" t="n">
-        <v>0.35416</v>
+        <v>0.126444</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -6924,7 +6924,7 @@
         <v>1</v>
       </c>
       <c r="G151" t="n">
-        <v>0.669109</v>
+        <v>0.634578</v>
       </c>
       <c r="H151" t="n">
         <v>0</v>
@@ -6967,7 +6967,7 @@
         <v>1</v>
       </c>
       <c r="G152" t="n">
-        <v>0.959183</v>
+        <v>0.894559</v>
       </c>
       <c r="H152" t="n">
         <v>0</v>
@@ -7010,7 +7010,7 @@
         <v>0</v>
       </c>
       <c r="G153" t="n">
-        <v>0.172402</v>
+        <v>0.179125</v>
       </c>
       <c r="H153" t="n">
         <v>0</v>
@@ -7053,7 +7053,7 @@
         <v>0</v>
       </c>
       <c r="G154" t="n">
-        <v>0.443312</v>
+        <v>0.303007</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
@@ -7096,7 +7096,7 @@
         <v>0</v>
       </c>
       <c r="G155" t="n">
-        <v>0.14218</v>
+        <v>0.176979</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -7139,7 +7139,7 @@
         <v>0</v>
       </c>
       <c r="G156" t="n">
-        <v>0.250197</v>
+        <v>0.231366</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -7182,7 +7182,7 @@
         <v>0</v>
       </c>
       <c r="G157" t="n">
-        <v>0.277235</v>
+        <v>0.278983</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -7225,7 +7225,7 @@
         <v>0</v>
       </c>
       <c r="G158" t="n">
-        <v>0.285869</v>
+        <v>0.13828</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -7268,7 +7268,7 @@
         <v>0</v>
       </c>
       <c r="G159" t="n">
-        <v>0.133752</v>
+        <v>0.154305</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -7311,7 +7311,7 @@
         <v>0</v>
       </c>
       <c r="G160" t="n">
-        <v>0.283863</v>
+        <v>0.140852</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -7354,7 +7354,7 @@
         <v>0</v>
       </c>
       <c r="G161" t="n">
-        <v>0.183319</v>
+        <v>0.118021</v>
       </c>
       <c r="H161" t="n">
         <v>0</v>
@@ -7397,7 +7397,7 @@
         <v>0</v>
       </c>
       <c r="G162" t="n">
-        <v>0.223775</v>
+        <v>0.245923</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
@@ -7440,7 +7440,7 @@
         <v>0</v>
       </c>
       <c r="G163" t="n">
-        <v>0.48552</v>
+        <v>0.463692</v>
       </c>
       <c r="H163" t="n">
         <v>0</v>
@@ -7483,7 +7483,7 @@
         <v>1</v>
       </c>
       <c r="G164" t="n">
-        <v>0.609478</v>
+        <v>0.5951379999999999</v>
       </c>
       <c r="H164" t="n">
         <v>0</v>
@@ -7526,7 +7526,7 @@
         <v>0</v>
       </c>
       <c r="G165" t="n">
-        <v>0.178416</v>
+        <v>0.14707</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -7569,7 +7569,7 @@
         <v>1</v>
       </c>
       <c r="G166" t="n">
-        <v>0.6124579999999999</v>
+        <v>0.769064</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
@@ -7612,7 +7612,7 @@
         <v>0</v>
       </c>
       <c r="G167" t="n">
-        <v>0.186246</v>
+        <v>0.148163</v>
       </c>
       <c r="H167" t="n">
         <v>0</v>
@@ -7655,7 +7655,7 @@
         <v>0</v>
       </c>
       <c r="G168" t="n">
-        <v>0.308678</v>
+        <v>0.356114</v>
       </c>
       <c r="H168" t="n">
         <v>0</v>
@@ -7698,7 +7698,7 @@
         <v>0</v>
       </c>
       <c r="G169" t="n">
-        <v>0.277738</v>
+        <v>0.271901</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -7741,7 +7741,7 @@
         <v>0</v>
       </c>
       <c r="G170" t="n">
-        <v>0.239803</v>
+        <v>0.182429</v>
       </c>
       <c r="H170" t="n">
         <v>0</v>
@@ -7784,7 +7784,7 @@
         <v>0</v>
       </c>
       <c r="G171" t="n">
-        <v>0.439939</v>
+        <v>0.250727</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -7827,7 +7827,7 @@
         <v>0</v>
       </c>
       <c r="G172" t="n">
-        <v>0.256377</v>
+        <v>0.162805</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
@@ -7870,7 +7870,7 @@
         <v>0</v>
       </c>
       <c r="G173" t="n">
-        <v>0.198416</v>
+        <v>0.13696</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -7913,7 +7913,7 @@
         <v>0</v>
       </c>
       <c r="G174" t="n">
-        <v>0.172044</v>
+        <v>0.091615</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -7956,7 +7956,7 @@
         <v>0</v>
       </c>
       <c r="G175" t="n">
-        <v>0.256013</v>
+        <v>0.240893</v>
       </c>
       <c r="H175" t="n">
         <v>0</v>
@@ -7999,7 +7999,7 @@
         <v>0</v>
       </c>
       <c r="G176" t="n">
-        <v>0.230709</v>
+        <v>0.10091</v>
       </c>
       <c r="H176" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
         <v>0</v>
       </c>
       <c r="G177" t="n">
-        <v>0.20708</v>
+        <v>0.154807</v>
       </c>
       <c r="H177" t="n">
         <v>0</v>
@@ -8085,7 +8085,7 @@
         <v>0</v>
       </c>
       <c r="G178" t="n">
-        <v>0.164287</v>
+        <v>0.19958</v>
       </c>
       <c r="H178" t="n">
         <v>0</v>
@@ -8128,7 +8128,7 @@
         <v>0</v>
       </c>
       <c r="G179" t="n">
-        <v>0.217442</v>
+        <v>0.23862</v>
       </c>
       <c r="H179" t="n">
         <v>0</v>
@@ -8171,7 +8171,7 @@
         <v>0</v>
       </c>
       <c r="G180" t="n">
-        <v>0.25245</v>
+        <v>0.229136</v>
       </c>
       <c r="H180" t="n">
         <v>0</v>
@@ -8214,7 +8214,7 @@
         <v>0</v>
       </c>
       <c r="G181" t="n">
-        <v>0.261953</v>
+        <v>0.235664</v>
       </c>
       <c r="H181" t="n">
         <v>0</v>
@@ -8257,7 +8257,7 @@
         <v>0</v>
       </c>
       <c r="G182" t="n">
-        <v>0.381368</v>
+        <v>0.176565</v>
       </c>
       <c r="H182" t="n">
         <v>0</v>
@@ -8300,7 +8300,7 @@
         <v>0</v>
       </c>
       <c r="G183" t="n">
-        <v>0.234114</v>
+        <v>0.255893</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
@@ -8343,7 +8343,7 @@
         <v>0</v>
       </c>
       <c r="G184" t="n">
-        <v>0.287414</v>
+        <v>0.269576</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
@@ -8386,7 +8386,7 @@
         <v>0</v>
       </c>
       <c r="G185" t="n">
-        <v>0.266675</v>
+        <v>0.204866</v>
       </c>
       <c r="H185" t="n">
         <v>0</v>
@@ -8429,7 +8429,7 @@
         <v>0</v>
       </c>
       <c r="G186" t="n">
-        <v>0.298707</v>
+        <v>0.203685</v>
       </c>
       <c r="H186" t="n">
         <v>0</v>
@@ -8472,7 +8472,7 @@
         <v>0</v>
       </c>
       <c r="G187" t="n">
-        <v>0.180603</v>
+        <v>0.143011</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
@@ -8515,7 +8515,7 @@
         <v>0</v>
       </c>
       <c r="G188" t="n">
-        <v>0.272949</v>
+        <v>0.489147</v>
       </c>
       <c r="H188" t="n">
         <v>0</v>
@@ -8558,7 +8558,7 @@
         <v>0</v>
       </c>
       <c r="G189" t="n">
-        <v>0.085616</v>
+        <v>0.097301</v>
       </c>
       <c r="H189" t="n">
         <v>0</v>
@@ -8601,7 +8601,7 @@
         <v>1</v>
       </c>
       <c r="G190" t="n">
-        <v>0.787855</v>
+        <v>0.76203</v>
       </c>
       <c r="H190" t="n">
         <v>1</v>
@@ -8641,10 +8641,10 @@
         <v>0.029019</v>
       </c>
       <c r="F191" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G191" t="n">
-        <v>0.614845</v>
+        <v>0.487627</v>
       </c>
       <c r="H191" t="n">
         <v>0</v>
@@ -8687,7 +8687,7 @@
         <v>0</v>
       </c>
       <c r="G192" t="n">
-        <v>0.359259</v>
+        <v>0.405572</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
@@ -8727,10 +8727,10 @@
         <v>0.027363</v>
       </c>
       <c r="F193" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G193" t="n">
-        <v>0.521722</v>
+        <v>0.291946</v>
       </c>
       <c r="H193" t="n">
         <v>0</v>
@@ -8773,7 +8773,7 @@
         <v>0</v>
       </c>
       <c r="G194" t="n">
-        <v>0.285846</v>
+        <v>0.164529</v>
       </c>
       <c r="H194" t="n">
         <v>0</v>
@@ -8816,7 +8816,7 @@
         <v>0</v>
       </c>
       <c r="G195" t="n">
-        <v>0.290464</v>
+        <v>0.178734</v>
       </c>
       <c r="H195" t="n">
         <v>0</v>
@@ -8859,7 +8859,7 @@
         <v>0</v>
       </c>
       <c r="G196" t="n">
-        <v>0.264303</v>
+        <v>0.23743</v>
       </c>
       <c r="H196" t="n">
         <v>0</v>
@@ -8902,7 +8902,7 @@
         <v>1</v>
       </c>
       <c r="G197" t="n">
-        <v>0.788086</v>
+        <v>0.647236</v>
       </c>
       <c r="H197" t="n">
         <v>0</v>
@@ -8945,7 +8945,7 @@
         <v>1</v>
       </c>
       <c r="G198" t="n">
-        <v>0.758975</v>
+        <v>0.660523</v>
       </c>
       <c r="H198" t="n">
         <v>0</v>
@@ -8988,7 +8988,7 @@
         <v>1</v>
       </c>
       <c r="G199" t="n">
-        <v>0.787844</v>
+        <v>0.818675</v>
       </c>
       <c r="H199" t="n">
         <v>0</v>
@@ -9031,7 +9031,7 @@
         <v>0</v>
       </c>
       <c r="G200" t="n">
-        <v>0.462395</v>
+        <v>0.41318</v>
       </c>
       <c r="H200" t="n">
         <v>0</v>
@@ -9074,7 +9074,7 @@
         <v>0</v>
       </c>
       <c r="G201" t="n">
-        <v>0.211075</v>
+        <v>0.1584</v>
       </c>
       <c r="H201" t="n">
         <v>0</v>
@@ -13933,7 +13933,7 @@
         <v>0</v>
       </c>
       <c r="G314" t="n">
-        <v>0.174096</v>
+        <v>0.148518</v>
       </c>
       <c r="H314" t="n">
         <v>0</v>
@@ -13976,7 +13976,7 @@
         <v>0</v>
       </c>
       <c r="G315" t="n">
-        <v>0.170578</v>
+        <v>0.181099</v>
       </c>
       <c r="H315" t="n">
         <v>0</v>
@@ -14019,7 +14019,7 @@
         <v>0</v>
       </c>
       <c r="G316" t="n">
-        <v>0.294943</v>
+        <v>0.271017</v>
       </c>
       <c r="H316" t="n">
         <v>0</v>
@@ -14062,7 +14062,7 @@
         <v>0</v>
       </c>
       <c r="G317" t="n">
-        <v>0.14311</v>
+        <v>0.183773</v>
       </c>
       <c r="H317" t="n">
         <v>0</v>
@@ -14105,7 +14105,7 @@
         <v>0</v>
       </c>
       <c r="G318" t="n">
-        <v>0.386114</v>
+        <v>0.468029</v>
       </c>
       <c r="H318" t="n">
         <v>0</v>
@@ -14148,7 +14148,7 @@
         <v>0</v>
       </c>
       <c r="G319" t="n">
-        <v>0.316625</v>
+        <v>0.412397</v>
       </c>
       <c r="H319" t="n">
         <v>0</v>
@@ -14191,7 +14191,7 @@
         <v>1</v>
       </c>
       <c r="G320" t="n">
-        <v>0.88202</v>
+        <v>0.841853</v>
       </c>
       <c r="H320" t="n">
         <v>0</v>
@@ -14234,7 +14234,7 @@
         <v>0</v>
       </c>
       <c r="G321" t="n">
-        <v>0.111809</v>
+        <v>0.116975</v>
       </c>
       <c r="H321" t="n">
         <v>0</v>
@@ -14277,7 +14277,7 @@
         <v>0</v>
       </c>
       <c r="G322" t="n">
-        <v>0.191651</v>
+        <v>0.249177</v>
       </c>
       <c r="H322" t="n">
         <v>0</v>
@@ -14320,7 +14320,7 @@
         <v>0</v>
       </c>
       <c r="G323" t="n">
-        <v>0.151357</v>
+        <v>0.08394500000000001</v>
       </c>
       <c r="H323" t="n">
         <v>0</v>
@@ -14363,7 +14363,7 @@
         <v>0</v>
       </c>
       <c r="G324" t="n">
-        <v>0.181583</v>
+        <v>0.308319</v>
       </c>
       <c r="H324" t="n">
         <v>0</v>
@@ -14406,7 +14406,7 @@
         <v>0</v>
       </c>
       <c r="G325" t="n">
-        <v>0.24191</v>
+        <v>0.136557</v>
       </c>
       <c r="H325" t="n">
         <v>0</v>
@@ -14449,7 +14449,7 @@
         <v>0</v>
       </c>
       <c r="G326" t="n">
-        <v>0.285525</v>
+        <v>0.192844</v>
       </c>
       <c r="H326" t="n">
         <v>0</v>
@@ -14492,7 +14492,7 @@
         <v>0</v>
       </c>
       <c r="G327" t="n">
-        <v>0.350148</v>
+        <v>0.244265</v>
       </c>
       <c r="H327" t="n">
         <v>0</v>
@@ -14535,7 +14535,7 @@
         <v>1</v>
       </c>
       <c r="G328" t="n">
-        <v>0.9123</v>
+        <v>0.947363</v>
       </c>
       <c r="H328" t="n">
         <v>0</v>
@@ -14578,7 +14578,7 @@
         <v>0</v>
       </c>
       <c r="G329" t="n">
-        <v>0.243066</v>
+        <v>0.251865</v>
       </c>
       <c r="H329" t="n">
         <v>0</v>
@@ -14621,7 +14621,7 @@
         <v>0</v>
       </c>
       <c r="G330" t="n">
-        <v>0.18525</v>
+        <v>0.106081</v>
       </c>
       <c r="H330" t="n">
         <v>0</v>
@@ -14664,7 +14664,7 @@
         <v>1</v>
       </c>
       <c r="G331" t="n">
-        <v>0.999027</v>
+        <v>0.997329</v>
       </c>
       <c r="H331" t="n">
         <v>1</v>
@@ -14707,7 +14707,7 @@
         <v>0</v>
       </c>
       <c r="G332" t="n">
-        <v>0.134979</v>
+        <v>0.081663</v>
       </c>
       <c r="H332" t="n">
         <v>0</v>
@@ -14750,7 +14750,7 @@
         <v>1</v>
       </c>
       <c r="G333" t="n">
-        <v>0.973482</v>
+        <v>0.9708059999999999</v>
       </c>
       <c r="H333" t="n">
         <v>1</v>
@@ -14790,10 +14790,10 @@
         <v>0.030285</v>
       </c>
       <c r="F334" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G334" t="n">
-        <v>0.47878</v>
+        <v>0.58509</v>
       </c>
       <c r="H334" t="n">
         <v>0</v>
@@ -14836,7 +14836,7 @@
         <v>0</v>
       </c>
       <c r="G335" t="n">
-        <v>0.160227</v>
+        <v>0.130082</v>
       </c>
       <c r="H335" t="n">
         <v>0</v>
@@ -14879,7 +14879,7 @@
         <v>0</v>
       </c>
       <c r="G336" t="n">
-        <v>0.497926</v>
+        <v>0.209082</v>
       </c>
       <c r="H336" t="n">
         <v>0</v>
@@ -14922,7 +14922,7 @@
         <v>0</v>
       </c>
       <c r="G337" t="n">
-        <v>0.11075</v>
+        <v>0.053103</v>
       </c>
       <c r="H337" t="n">
         <v>0</v>
@@ -14965,7 +14965,7 @@
         <v>0</v>
       </c>
       <c r="G338" t="n">
-        <v>0.183074</v>
+        <v>0.121718</v>
       </c>
       <c r="H338" t="n">
         <v>0</v>
@@ -15008,7 +15008,7 @@
         <v>0</v>
       </c>
       <c r="G339" t="n">
-        <v>0.164029</v>
+        <v>0.075825</v>
       </c>
       <c r="H339" t="n">
         <v>0</v>
@@ -15051,7 +15051,7 @@
         <v>0</v>
       </c>
       <c r="G340" t="n">
-        <v>0.440357</v>
+        <v>0.200476</v>
       </c>
       <c r="H340" t="n">
         <v>0</v>
@@ -15094,7 +15094,7 @@
         <v>0</v>
       </c>
       <c r="G341" t="n">
-        <v>0.352609</v>
+        <v>0.202148</v>
       </c>
       <c r="H341" t="n">
         <v>0</v>
@@ -15137,7 +15137,7 @@
         <v>0</v>
       </c>
       <c r="G342" t="n">
-        <v>0.19459</v>
+        <v>0.067611</v>
       </c>
       <c r="H342" t="n">
         <v>0</v>
@@ -15180,7 +15180,7 @@
         <v>0</v>
       </c>
       <c r="G343" t="n">
-        <v>0.079067</v>
+        <v>0.056275</v>
       </c>
       <c r="H343" t="n">
         <v>0</v>
@@ -15223,7 +15223,7 @@
         <v>0</v>
       </c>
       <c r="G344" t="n">
-        <v>0.104081</v>
+        <v>0.040926</v>
       </c>
       <c r="H344" t="n">
         <v>0</v>
@@ -15266,7 +15266,7 @@
         <v>0</v>
       </c>
       <c r="G345" t="n">
-        <v>0.297698</v>
+        <v>0.312142</v>
       </c>
       <c r="H345" t="n">
         <v>0</v>
@@ -15309,7 +15309,7 @@
         <v>0</v>
       </c>
       <c r="G346" t="n">
-        <v>0.196089</v>
+        <v>0.113856</v>
       </c>
       <c r="H346" t="n">
         <v>0</v>
@@ -15352,7 +15352,7 @@
         <v>0</v>
       </c>
       <c r="G347" t="n">
-        <v>0.269956</v>
+        <v>0.212454</v>
       </c>
       <c r="H347" t="n">
         <v>0</v>
@@ -15395,7 +15395,7 @@
         <v>0</v>
       </c>
       <c r="G348" t="n">
-        <v>0.449854</v>
+        <v>0.327036</v>
       </c>
       <c r="H348" t="n">
         <v>0</v>
@@ -15435,10 +15435,10 @@
         <v>0.0188</v>
       </c>
       <c r="F349" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G349" t="n">
-        <v>0.649914</v>
+        <v>0.450212</v>
       </c>
       <c r="H349" t="n">
         <v>1</v>
@@ -15481,7 +15481,7 @@
         <v>1</v>
       </c>
       <c r="G350" t="n">
-        <v>0.8882060000000001</v>
+        <v>0.990695</v>
       </c>
       <c r="H350" t="n">
         <v>0</v>
@@ -15521,10 +15521,10 @@
         <v>0.007157</v>
       </c>
       <c r="F351" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G351" t="n">
-        <v>0.446328</v>
+        <v>0.592908</v>
       </c>
       <c r="H351" t="n">
         <v>0</v>
@@ -15564,10 +15564,10 @@
         <v>0.001027</v>
       </c>
       <c r="F352" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G352" t="n">
-        <v>0.572953</v>
+        <v>0.423374</v>
       </c>
       <c r="H352" t="n">
         <v>0</v>
@@ -15610,7 +15610,7 @@
         <v>0</v>
       </c>
       <c r="G353" t="n">
-        <v>0.177081</v>
+        <v>0.106128</v>
       </c>
       <c r="H353" t="n">
         <v>0</v>
@@ -15653,7 +15653,7 @@
         <v>0</v>
       </c>
       <c r="G354" t="n">
-        <v>0.239963</v>
+        <v>0.309265</v>
       </c>
       <c r="H354" t="n">
         <v>0</v>
@@ -15696,7 +15696,7 @@
         <v>0</v>
       </c>
       <c r="G355" t="n">
-        <v>0.15202</v>
+        <v>0.169344</v>
       </c>
       <c r="H355" t="n">
         <v>0</v>
@@ -15739,7 +15739,7 @@
         <v>0</v>
       </c>
       <c r="G356" t="n">
-        <v>0.085922</v>
+        <v>0.089208</v>
       </c>
       <c r="H356" t="n">
         <v>0</v>
@@ -15782,7 +15782,7 @@
         <v>0</v>
       </c>
       <c r="G357" t="n">
-        <v>0.08204699999999999</v>
+        <v>0.188372</v>
       </c>
       <c r="H357" t="n">
         <v>0</v>
@@ -15825,7 +15825,7 @@
         <v>1</v>
       </c>
       <c r="G358" t="n">
-        <v>0.692365</v>
+        <v>0.613469</v>
       </c>
       <c r="H358" t="n">
         <v>0</v>
@@ -15868,7 +15868,7 @@
         <v>0</v>
       </c>
       <c r="G359" t="n">
-        <v>0.069966</v>
+        <v>0.073495</v>
       </c>
       <c r="H359" t="n">
         <v>0</v>
@@ -15908,10 +15908,10 @@
         <v>0.032339</v>
       </c>
       <c r="F360" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G360" t="n">
-        <v>0.491959</v>
+        <v>0.784481</v>
       </c>
       <c r="H360" t="n">
         <v>0</v>
@@ -15954,7 +15954,7 @@
         <v>1</v>
       </c>
       <c r="G361" t="n">
-        <v>0.648003</v>
+        <v>0.656824</v>
       </c>
       <c r="H361" t="n">
         <v>0</v>
@@ -15997,7 +15997,7 @@
         <v>1</v>
       </c>
       <c r="G362" t="n">
-        <v>0.861326</v>
+        <v>0.7612910000000001</v>
       </c>
       <c r="H362" t="n">
         <v>0</v>
@@ -16040,7 +16040,7 @@
         <v>0</v>
       </c>
       <c r="G363" t="n">
-        <v>0.13267</v>
+        <v>0.108364</v>
       </c>
       <c r="H363" t="n">
         <v>0</v>
@@ -16083,7 +16083,7 @@
         <v>1</v>
       </c>
       <c r="G364" t="n">
-        <v>0.895248</v>
+        <v>0.939364</v>
       </c>
       <c r="H364" t="n">
         <v>0</v>
@@ -16126,7 +16126,7 @@
         <v>0</v>
       </c>
       <c r="G365" t="n">
-        <v>0.282903</v>
+        <v>0.191559</v>
       </c>
       <c r="H365" t="n">
         <v>0</v>
@@ -16169,7 +16169,7 @@
         <v>0</v>
       </c>
       <c r="G366" t="n">
-        <v>0.298909</v>
+        <v>0.193907</v>
       </c>
       <c r="H366" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
         <v>0</v>
       </c>
       <c r="G367" t="n">
-        <v>0.480375</v>
+        <v>0.44266</v>
       </c>
       <c r="H367" t="n">
         <v>0</v>
@@ -16255,7 +16255,7 @@
         <v>0</v>
       </c>
       <c r="G368" t="n">
-        <v>0.306588</v>
+        <v>0.419903</v>
       </c>
       <c r="H368" t="n">
         <v>0</v>
@@ -16298,7 +16298,7 @@
         <v>0</v>
       </c>
       <c r="G369" t="n">
-        <v>0.267147</v>
+        <v>0.439807</v>
       </c>
       <c r="H369" t="n">
         <v>0</v>
@@ -16341,7 +16341,7 @@
         <v>0</v>
       </c>
       <c r="G370" t="n">
-        <v>0.390077</v>
+        <v>0.192044</v>
       </c>
       <c r="H370" t="n">
         <v>0</v>
@@ -16381,10 +16381,10 @@
         <v>0.159232</v>
       </c>
       <c r="F371" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G371" t="n">
-        <v>0.518286</v>
+        <v>0.247779</v>
       </c>
       <c r="H371" t="n">
         <v>0</v>
@@ -16424,10 +16424,10 @@
         <v>0.009669000000000001</v>
       </c>
       <c r="F372" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G372" t="n">
-        <v>0.545351</v>
+        <v>0.31839</v>
       </c>
       <c r="H372" t="n">
         <v>0</v>
@@ -16470,7 +16470,7 @@
         <v>0</v>
       </c>
       <c r="G373" t="n">
-        <v>0.429066</v>
+        <v>0.431673</v>
       </c>
       <c r="H373" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
         <v>1</v>
       </c>
       <c r="G374" t="n">
-        <v>0.566835</v>
+        <v>0.586184</v>
       </c>
       <c r="H374" t="n">
         <v>0</v>
@@ -16556,7 +16556,7 @@
         <v>0</v>
       </c>
       <c r="G375" t="n">
-        <v>0.185022</v>
+        <v>0.239388</v>
       </c>
       <c r="H375" t="n">
         <v>0</v>
@@ -16599,7 +16599,7 @@
         <v>0</v>
       </c>
       <c r="G376" t="n">
-        <v>0.451642</v>
+        <v>0.218037</v>
       </c>
       <c r="H376" t="n">
         <v>0</v>
@@ -16642,7 +16642,7 @@
         <v>0</v>
       </c>
       <c r="G377" t="n">
-        <v>0.33415</v>
+        <v>0.31385</v>
       </c>
       <c r="H377" t="n">
         <v>0</v>
@@ -16685,7 +16685,7 @@
         <v>0</v>
       </c>
       <c r="G378" t="n">
-        <v>0.309813</v>
+        <v>0.354608</v>
       </c>
       <c r="H378" t="n">
         <v>0</v>
@@ -16728,7 +16728,7 @@
         <v>0</v>
       </c>
       <c r="G379" t="n">
-        <v>0.218718</v>
+        <v>0.324129</v>
       </c>
       <c r="H379" t="n">
         <v>0</v>
@@ -16768,10 +16768,10 @@
         <v>0.047454</v>
       </c>
       <c r="F380" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G380" t="n">
-        <v>0.395446</v>
+        <v>0.725603</v>
       </c>
       <c r="H380" t="n">
         <v>0</v>
@@ -16814,7 +16814,7 @@
         <v>0</v>
       </c>
       <c r="G381" t="n">
-        <v>0.347191</v>
+        <v>0.449793</v>
       </c>
       <c r="H381" t="n">
         <v>0</v>
@@ -16857,7 +16857,7 @@
         <v>0</v>
       </c>
       <c r="G382" t="n">
-        <v>0.305736</v>
+        <v>0.421452</v>
       </c>
       <c r="H382" t="n">
         <v>0</v>
@@ -16900,7 +16900,7 @@
         <v>0</v>
       </c>
       <c r="G383" t="n">
-        <v>0.166512</v>
+        <v>0.132052</v>
       </c>
       <c r="H383" t="n">
         <v>0</v>
@@ -16943,7 +16943,7 @@
         <v>0</v>
       </c>
       <c r="G384" t="n">
-        <v>0.14286</v>
+        <v>0.12667</v>
       </c>
       <c r="H384" t="n">
         <v>0</v>
@@ -16986,7 +16986,7 @@
         <v>0</v>
       </c>
       <c r="G385" t="n">
-        <v>0.17294</v>
+        <v>0.117023</v>
       </c>
       <c r="H385" t="n">
         <v>0</v>
@@ -17029,7 +17029,7 @@
         <v>0</v>
       </c>
       <c r="G386" t="n">
-        <v>0.204823</v>
+        <v>0.120341</v>
       </c>
       <c r="H386" t="n">
         <v>0</v>
@@ -17072,7 +17072,7 @@
         <v>0</v>
       </c>
       <c r="G387" t="n">
-        <v>0.225718</v>
+        <v>0.180723</v>
       </c>
       <c r="H387" t="n">
         <v>0</v>
@@ -17115,7 +17115,7 @@
         <v>0</v>
       </c>
       <c r="G388" t="n">
-        <v>0.23135</v>
+        <v>0.264927</v>
       </c>
       <c r="H388" t="n">
         <v>0</v>
@@ -17158,7 +17158,7 @@
         <v>0</v>
       </c>
       <c r="G389" t="n">
-        <v>0.161455</v>
+        <v>0.18285</v>
       </c>
       <c r="H389" t="n">
         <v>0</v>
@@ -17201,7 +17201,7 @@
         <v>0</v>
       </c>
       <c r="G390" t="n">
-        <v>0.411579</v>
+        <v>0.4554</v>
       </c>
       <c r="H390" t="n">
         <v>0</v>
@@ -17244,7 +17244,7 @@
         <v>0</v>
       </c>
       <c r="G391" t="n">
-        <v>0.272199</v>
+        <v>0.294842</v>
       </c>
       <c r="H391" t="n">
         <v>0</v>
@@ -17287,7 +17287,7 @@
         <v>0</v>
       </c>
       <c r="G392" t="n">
-        <v>0.467431</v>
+        <v>0.416957</v>
       </c>
       <c r="H392" t="n">
         <v>0</v>
@@ -17330,7 +17330,7 @@
         <v>1</v>
       </c>
       <c r="G393" t="n">
-        <v>0.868028</v>
+        <v>0.891539</v>
       </c>
       <c r="H393" t="n">
         <v>1</v>
@@ -17373,7 +17373,7 @@
         <v>0</v>
       </c>
       <c r="G394" t="n">
-        <v>0.164409</v>
+        <v>0.171394</v>
       </c>
       <c r="H394" t="n">
         <v>0</v>
@@ -17416,7 +17416,7 @@
         <v>1</v>
       </c>
       <c r="G395" t="n">
-        <v>0.523424</v>
+        <v>0.556195</v>
       </c>
       <c r="H395" t="n">
         <v>0</v>
@@ -17459,7 +17459,7 @@
         <v>0</v>
       </c>
       <c r="G396" t="n">
-        <v>0.331406</v>
+        <v>0.249616</v>
       </c>
       <c r="H396" t="n">
         <v>0</v>
@@ -17502,7 +17502,7 @@
         <v>1</v>
       </c>
       <c r="G397" t="n">
-        <v>0.684567</v>
+        <v>0.621931</v>
       </c>
       <c r="H397" t="n">
         <v>0</v>
@@ -17545,7 +17545,7 @@
         <v>0</v>
       </c>
       <c r="G398" t="n">
-        <v>0.401513</v>
+        <v>0.247449</v>
       </c>
       <c r="H398" t="n">
         <v>0</v>
@@ -17588,7 +17588,7 @@
         <v>0</v>
       </c>
       <c r="G399" t="n">
-        <v>0.296611</v>
+        <v>0.150968</v>
       </c>
       <c r="H399" t="n">
         <v>0</v>
@@ -17631,7 +17631,7 @@
         <v>0</v>
       </c>
       <c r="G400" t="n">
-        <v>0.22139</v>
+        <v>0.488095</v>
       </c>
       <c r="H400" t="n">
         <v>0</v>
@@ -17674,7 +17674,7 @@
         <v>0</v>
       </c>
       <c r="G401" t="n">
-        <v>0.21971</v>
+        <v>0.338361</v>
       </c>
       <c r="H401" t="n">
         <v>0</v>
@@ -17717,7 +17717,7 @@
         <v>0</v>
       </c>
       <c r="G402" t="n">
-        <v>0.140178</v>
+        <v>0.142357</v>
       </c>
       <c r="H402" t="n">
         <v>0</v>
@@ -17760,7 +17760,7 @@
         <v>1</v>
       </c>
       <c r="G403" t="n">
-        <v>0.878673</v>
+        <v>0.953134</v>
       </c>
       <c r="H403" t="n">
         <v>1</v>
@@ -17803,7 +17803,7 @@
         <v>0</v>
       </c>
       <c r="G404" t="n">
-        <v>0.156075</v>
+        <v>0.113676</v>
       </c>
       <c r="H404" t="n">
         <v>0</v>
@@ -17846,7 +17846,7 @@
         <v>0</v>
       </c>
       <c r="G405" t="n">
-        <v>0.083139</v>
+        <v>0.083283</v>
       </c>
       <c r="H405" t="n">
         <v>0</v>
@@ -17889,7 +17889,7 @@
         <v>0</v>
       </c>
       <c r="G406" t="n">
-        <v>0.178847</v>
+        <v>0.216749</v>
       </c>
       <c r="H406" t="n">
         <v>0</v>
@@ -17929,10 +17929,10 @@
         <v>0.061152</v>
       </c>
       <c r="F407" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G407" t="n">
-        <v>0.5877</v>
+        <v>0.440575</v>
       </c>
       <c r="H407" t="n">
         <v>0</v>
@@ -17975,7 +17975,7 @@
         <v>1</v>
       </c>
       <c r="G408" t="n">
-        <v>0.987085</v>
+        <v>0.978808</v>
       </c>
       <c r="H408" t="n">
         <v>0</v>
@@ -18018,7 +18018,7 @@
         <v>0</v>
       </c>
       <c r="G409" t="n">
-        <v>0.344067</v>
+        <v>0.199346</v>
       </c>
       <c r="H409" t="n">
         <v>0</v>
@@ -18061,7 +18061,7 @@
         <v>0</v>
       </c>
       <c r="G410" t="n">
-        <v>0.121179</v>
+        <v>0.093852</v>
       </c>
       <c r="H410" t="n">
         <v>0</v>
@@ -18101,10 +18101,10 @@
         <v>0.005633</v>
       </c>
       <c r="F411" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G411" t="n">
-        <v>0.540639</v>
+        <v>0.393607</v>
       </c>
       <c r="H411" t="n">
         <v>0</v>
@@ -18147,7 +18147,7 @@
         <v>0</v>
       </c>
       <c r="G412" t="n">
-        <v>0.303403</v>
+        <v>0.392735</v>
       </c>
       <c r="H412" t="n">
         <v>0</v>
@@ -18190,7 +18190,7 @@
         <v>0</v>
       </c>
       <c r="G413" t="n">
-        <v>0.156028</v>
+        <v>0.17765</v>
       </c>
       <c r="H413" t="n">
         <v>0</v>
@@ -18233,7 +18233,7 @@
         <v>1</v>
       </c>
       <c r="G414" t="n">
-        <v>0.786095</v>
+        <v>0.895952</v>
       </c>
       <c r="H414" t="n">
         <v>0</v>
